--- a/learning/workshop.xlsx
+++ b/learning/workshop.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\swaper\learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80F0C1A-36A1-4FD6-A063-970954F71AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44564D3C-EE2A-44FB-BCEB-780070864B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F1C148BE-D835-4679-8BE0-C794BD7A9454}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>Dates</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>https://gscb.hcdc.vn/index.php/s/ZbQpSkm7ETwyfG5</t>
+  </si>
+  <si>
+    <t>https://gscb.hcdc.vn/index.php/s/QC6Bq9rMZ2Kb2a9</t>
+  </si>
+  <si>
+    <t>An Tran, Anh Huynh, Thu Pham</t>
+  </si>
+  <si>
+    <t>DART Pipeline</t>
   </si>
 </sst>
 </file>
@@ -514,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0317A4F8-CCD3-4004-9B3B-6F021BB3E9FA}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1" bestFit="1" customWidth="1"/>
@@ -677,6 +686,23 @@
         <v>29</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{B97DF487-9103-45F6-962F-49055245C283}"/>
@@ -687,6 +713,7 @@
     <hyperlink ref="E7" r:id="rId6" xr:uid="{FD4938CB-0E54-4E84-906C-492C86032635}"/>
     <hyperlink ref="E8" r:id="rId7" xr:uid="{AF398148-A33F-46B7-B48F-01E786D367C0}"/>
     <hyperlink ref="E9" r:id="rId8" xr:uid="{BD7476E8-B4BC-4F63-A660-5EC26DE1ECF1}"/>
+    <hyperlink ref="E10" r:id="rId9" xr:uid="{E6D0B02A-06DB-45BF-93B8-767A8FB7484B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
